--- a/plantilla/mcu5/excel/02-registro-activos-mcu5.xlsx
+++ b/plantilla/mcu5/excel/02-registro-activos-mcu5.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Activos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Activos" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -523,600 +523,862 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>A01</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Servidor de control central</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Cliente-gestor (app de escritorio)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>HW/SW</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>VM con el control central (API + dashboard)</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Aplicacion Tauri (Rust + React) que opera la boveda de forma local</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Estacion del usuario</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Usuario final</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Confidencial</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Gestion de credenciales</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Proteger</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>4 GB RAM minimo (RNF-02); no requiere red para operar</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Boveda cifrada del usuario</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Dato</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Archivo local con credenciales cifradas (Argon2id + XChaCha20-Poly1305)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Estacion del usuario</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Usuario final</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Secreto</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Muy alta</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Acceso a sistemas</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Proteger</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Nunca sale del cliente (zero-knowledge)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>A03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Clave privada de firma de eventos</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Dato</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Clave JWS por agente para firmar eventos de auditoria</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Estacion del usuario (keystore local)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Secreto</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Auditoria</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Proteger/Detectar</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Unica por agente: evita forjar eventos de otro cliente</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>A04</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Servidor control-central</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>HW/SW</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>API FastAPI en contenedor Docker: recibe eventos, RBAC, dashboard API</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>VLAN Servidores</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Confidencial</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Gestión de secretos</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Gestion de secretos/auditoria</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>Proteger/Detectar</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>A02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>PostgreSQL (eventos)</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Ver docs/00-arquitectura-c4.md nivel 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>A05</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PostgreSQL (control-central)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>Dato</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Base de eventos de auditoría</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Servidor control</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Persistencia de eventos, usuarios del panel e incidentes</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Servidor control-central</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Confidencial</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Auditoría</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Auditoria</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Detectar</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>Retención 90+ días</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>A03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Bóveda en cliente</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Retencion &gt;= 90 dias (RNF-07)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A06</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Claves publicas de agentes</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>Dato</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Bóveda cifrada de credenciales</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Estación usuario</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Usuario</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Claves usadas por control-central para verificar la firma JWS de cada cliente</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Servidor control-central</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Interno</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Auditoria</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Proteger</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>No permite descifrar ni firmar, solo verificar</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A07</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Base de usuarios del panel (RBAC)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Dato</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Usuarios del control central con rol y MFA (Argon2id/bcrypt)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PostgreSQL control-central</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>Secreto</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Muy alta</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Acceso a sistemas</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Gestion de accesos</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>Proteger</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>Solo cliente</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>A04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Servidor SIEM</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Algoritmo de hash elegible (RF-11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A08</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Servidor Wazuh (manager + indexer + dashboard)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>HW/SW</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Wazuh / Elastic (correlación)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>SIEM/HIDS: correlacion y reglas de deteccion</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
         <is>
           <t>VLAN Seguridad</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Confidencial</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Monitoreo</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Monitoreo/Deteccion</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>Detectar</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>A05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Servidor de correo</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Reglas: fuerza bruta de maestra, borrado masivo, cambio de maestra</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A09</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Agentes Wazuh (en clientes)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>SW</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Integridad de archivos (FIM) sobre el archivo de boveda</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Estaciones de usuario</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Interno</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Monitoreo de hosts</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Detectar</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Servidor de correo Mailu</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>HW/SW</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Postfix/Dovecot (SMTP)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Postfix + Dovecot + Rspamd: envio de notificaciones</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
         <is>
           <t>VLAN Servicios</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>Interno</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Media</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>Notificaciones</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>Responder</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>A06</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Firewall de perímetro</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>SPF/DKIM/DMARC configurados (mitiga RT-04)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dashboard Grafana</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>HW/SW</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>OPNsense con VLANs y reglas</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Perímetro</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>KPIs, alertas, incidentes, estado de agentes</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Servidor control-central</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Interno</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Monitoreo/KPIs</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Detectar/Gobernar</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Gestion de incidentes (TheHive o tabla interna)</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HW/SW</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ciclo de vida de incidentes: abierto/en analisis/resuelto</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Servidor control-central</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Interno</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Media</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Respuesta a incidentes</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Responder</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Decision abierta: ver docs/99-bitacora-trabajo.md (15/09/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>A13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Repositorio Git (codigo fuente)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>SW/Dato</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Codigo de cliente-gestor, control-central e infra</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>GitHub: varelafervenza/tsi-obligatorio</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blue Team</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Interno</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Desarrollo/Trazabilidad</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Gobernar</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Tag v1.0 + hash SHA-256 en pre-entrega (07/10/2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>A14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Segmentacion de red del laboratorio</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HW</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VLANs/firewall entre estacion cliente, control-central, SIEM y correo</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Perimetro del laboratorio</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>Confidencial</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Red</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>Proteger</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>A07</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>NIDS</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>HW/SW</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Suricata/Zeek (mirror de tráfico)</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>VLAN Seguridad</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>RSI</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Confidencial</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Alta</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Detección</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>Detectar</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>A08</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Base de datos de clientes</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Dato</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Datos personales de usuarios</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>Servidor control</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>RSI</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Secreto</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>Muy alta</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Auditoría</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>Identificar/Proteger</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>Registro URCDP</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>A09</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Llave maestra / certificados</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Dato</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Material criptográfico</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>HSM/cofre local</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>RSI</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Secreto</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Muy alta</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Criptografía</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>Proteger</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>Rotación definida</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>A10</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Agentes HIDS (clientes)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>SW</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Agentes Wazuh en estaciones</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>Estaciones</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>RSI</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Interno</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Media</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>Monitoreo de hosts</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Detectar</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>IPs/VLANs reales pendientes (Anexo A de LETRA.md)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
